--- a/results/Int Task Remove ACC 0.6/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC 0.6/Rando_4_permute.xlsx
@@ -440,277 +440,277 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7083768647650517</v>
+        <v>0.7338549006268527</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.731128618170627</v>
+        <v>0.7518222459789106</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7385562952524418</v>
+        <v>0.7501032606054716</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7344035991382801</v>
+        <v>0.7453188525519543</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.725782350940279</v>
+        <v>0.7276906474237492</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7030073132805287</v>
+        <v>0.7167885546754782</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6904793721755187</v>
+        <v>0.7151859905729141</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7022824643244732</v>
+        <v>0.6931590861233944</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7297720572752158</v>
+        <v>0.6931590861233944</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.713407276025722</v>
+        <v>0.6925273741840388</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6803618575570565</v>
+        <v>0.6751917407713365</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7279133663767271</v>
+        <v>0.6751917407713365</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7350019032346891</v>
+        <v>0.6783968689764647</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6236069941850106</v>
+        <v>0.6783968689764647</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6264031294037611</v>
+        <v>0.6961182111213697</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6215954370960688</v>
+        <v>0.6986916273871422</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5901991512383173</v>
+        <v>0.6986916273871422</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5885965871357532</v>
+        <v>0.6960949268671948</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5776712101333075</v>
+        <v>0.720519097137859</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.585684030646128</v>
+        <v>0.7906694931726517</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5808763383384357</v>
+        <v>0.7887510731004098</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5754369340913876</v>
+        <v>0.7884352171307319</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5664532614153587</v>
+        <v>0.7877103681746764</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5840814665435639</v>
+        <v>0.7862242253429872</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5616455691076664</v>
+        <v>0.7833582373617118</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5616455691076664</v>
+        <v>0.7785738293081945</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5664532614153587</v>
+        <v>0.7785738293081945</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5648506973127946</v>
+        <v>0.7760236972965968</v>
       </c>
     </row>
     <row r="30">
@@ -720,77 +720,77 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5568378767999741</v>
+        <v>0.7722334256604629</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5590721528418938</v>
+        <v>0.775731125581094</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5590721528418938</v>
+        <v>0.5138612177462462</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5590721528418938</v>
+        <v>0.5109719455107957</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5587562968722161</v>
+        <v>0.5100010933475874</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5654824092521502</v>
+        <v>0.4913423068824206</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5654824092521502</v>
+        <v>0.4919973030759512</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5616222848534914</v>
+        <v>0.490863461133518</v>
       </c>
     </row>
     <row r="38">
@@ -800,333 +800,333 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5734952297649708</v>
+        <v>0.4975430050051023</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5750745096133599</v>
+        <v>0.522938027438975</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5782796378184881</v>
+        <v>0.5376536760775548</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5670384048463644</v>
+        <v>0.5405196640588302</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5657749809676531</v>
+        <v>0.4915417415812235</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5128903655830378</v>
+        <v>0.4924660252360821</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5128903655830378</v>
+        <v>0.4905708894180151</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5096852373779095</v>
+        <v>0.4905708894180151</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5096852373779095</v>
+        <v>0.4987365761212887</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5096852373779095</v>
+        <v>0.4977890082122552</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.4984207201516109</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4984207201516109</v>
+        <v>0.4933670246367656</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4965255843335439</v>
+        <v>0.4955780164245104</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4962097283638661</v>
+        <v>0.4955780164245104</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4971572962728996</v>
+        <v>0.4933903088909406</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4968414403032217</v>
+        <v>0.4930744529212628</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4971572962728996</v>
+        <v>0.4940453050844712</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4984207201516109</v>
+        <v>0.4995545620940441</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4974731522425774</v>
+        <v>0.5110185140191458</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4987598603754637</v>
+        <v>0.5025967005199475</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4987598603754637</v>
+        <v>0.5065033934269563</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4959870094108881</v>
+        <v>0.5081525260378703</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4991688533618414</v>
+        <v>0.5058716814876006</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5013565608954111</v>
+        <v>0.4965488685877189</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5013565608954111</v>
+        <v>0.4996841440303222</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.501649132610914</v>
+        <v>0.4996841440303222</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5019649885805919</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5019649885805919</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5025734162657726</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5025734162657726</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5025734162657726</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1136,7 +1136,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1146,77 +1146,77 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4990524320909665</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5009708521632085</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4984207201516109</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4984207201516109</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5009708521632085</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1226,17 +1226,17 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5012867081328863</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1246,7 +1246,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1256,7 +1256,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1266,7 +1266,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1276,7 +1276,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1286,7 +1286,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1296,7 +1296,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1306,7 +1306,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1316,7 +1316,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
